--- a/output/第10期計画_趨勢に現れない要因の分析.xlsx
+++ b/output/第10期計画_趨勢に現れない要因の分析.xlsx
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>令和9年度は改定の年に当たりますが改定率は未告示です。当区域の単価指数は7年で+12.93％（年率+1.75％）伸びており、改定のあった年（平均+1.42％）となかった年（平均+2.20％）で差が見られません。利用日数・回数の伸びは年率+0.25％にとどまるため、残りは報酬改定・加算の算定・要介護度の重度化によるものです。単価を固定していることは月額で+244円から+327円に当たります。</t>
+          <t>令和9年度は改定の年に当たりますが改定率は未告示です。加えて令和8年度にも改定が行われるため、令和7年度の単価を固定すると2回分の改定を落とすことになります。当区域の単価指数は7年で+12.93％（年率+1.75％）伸びており、改定のあった年（平均+1.42％）となかった年（平均+2.20％）で差が見られません。利用日数・回数の伸びは年率+0.25％にとどまるため、残りは報酬改定・加算の算定・要介護度の重度化によるものです。単価を固定していることは月額で+244円から+327円に当たります。</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -3365,7 +3365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3564,95 +3564,97 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>令和9年度</t>
+          <t>令和8年度</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>改定（見込み）</t>
+          <t>改定</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第10期の初年度</t>
+          <t>第9期の最終年度</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
+          <t>令和9年度改定を待たずに実施。職員の処遇改善、生産性向上・協働化の促進等のため。改定率は未告示［要確認］</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>改定（見込み）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>第10期の初年度</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
           <t>改定率は未告示［要確認］</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>注）介護報酬の改定は3年ごとに行われ、介護保険事業計画の期間と同期しています。令和9年度は第10期の初年度であり、改定の年に当たります。
-「構成町の意見への回答と工程の前倒し案」の「第10期は令和9年度が改定の年に当たらない」との記述は誤りであり、本作業で修正しました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>注1）介護報酬の改定は3年ごとに行われ、介護保険事業計画の期間と同期しています。令和9年度は第10期の初年度であり、改定の年に当たります。
+注2）これに加えて、令和8年度に改定が行われることが令和8年3月の全国課長会議資料に示されています（「令和9年度介護報酬改定を待たずに…令和8年度介護報酬改定を行う」）。
+注3）当方の算定は令和7年度の単価を固定しているため、令和8年度改定と令和9年度改定の2回分が織り込まれていません。改定率1％当たりの効きは1回分の値であり、2回分では倍になります。
+注4）「構成町の意見への回答と工程の前倒し案」の「第10期は令和9年度が改定の年に当たらない」との記述は誤りであり、本作業で修正しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2　当区域の単価の実績（構成を固定した指数）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>単価指数</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>対前年</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>改定の有無</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>H30</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>改定（平成30年4月）</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>基準</t>
         </is>
       </c>
     </row>
@@ -3660,43 +3662,47 @@
       <c r="A17" s="6" t="inlineStr"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>R元</t>
+          <t>H30</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>101.317</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>+1.32％</t>
+        <v>100</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>改定（令和元年10月・半年分）</t>
+          <t>改定（平成30年4月）</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R元</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>104.12</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>+2.77％</t>
+        <v>101.317</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+1.32％</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>改定（令和元年10月・半年分）</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -3706,20 +3712,20 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>105.354</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>+1.18％</t>
+        <v>104.12</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>+2.77％</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>改定（令和3年4月）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -3729,20 +3735,20 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>106.558</v>
+        <v>105.354</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>+1.14％</t>
+          <t>+1.18％</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>加算（令和4年10月・半年分）</t>
+          <t>改定（令和3年4月）</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
@@ -3752,20 +3758,20 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>107.705</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>+1.08％</t>
+        <v>106.558</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>+1.14％</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>加算（令和4年10月・半年分）</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -3775,20 +3781,20 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>109.893</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>+2.03％</t>
+        <v>107.705</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>+1.08％</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>改定（令和6年4月）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
@@ -3798,54 +3804,77 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>112.929</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>+2.76％</t>
+        <v>109.893</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>+2.03％</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>改定（令和6年4月）</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="11" t="inlineStr"/>
-      <c r="B24" s="11" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>112.929</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>+2.76％</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>7年計</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C25" s="12" t="n">
         <v>112.929</v>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>+12.93％</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>年率+1.75％</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>中央値+1.32％</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="62" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>注1）単価指数は、前年の利用者構成で固定した連鎖ラスパイレス指数です。　　指数＝Σ(前年の利用者数×当年の1人あたり給付費)÷Σ(前年の利用者数×前年の1人あたり給付費)
 注2）構成を固定しないと、単価の低い在宅サービスの比重が上がることにより総額の単価が下がり、改定の効果が見えなくなります。
@@ -3853,77 +3882,52 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>3　単価の伸びの内訳</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>年率</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>測り方</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>単価（1人あたり給付費）</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>+1.75％</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>構成を固定した連鎖ラスパイレス指数</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>報酬改定・加算の算定・要介護度の重度化・利用量の合計</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり利用日数・回数</t>
+          <t>単価（1人あたり給付費）</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>+0.25％</t>
+          <t>+1.75％</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>総括表詳細（３）の14系列の中央値（平成30年度→令和7年度）</t>
+          <t>構成を固定した連鎖ラスパイレス指数</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
@@ -3931,24 +3935,24 @@
       <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>利用量による分</t>
+          <t>報酬改定・加算の算定・要介護度の重度化・利用量の合計</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>差（利用量以外の分）</t>
+          <t>1人1月あたり利用日数・回数</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>+1.51％</t>
+          <t>+0.25％</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>上の2つの差</t>
+          <t>総括表詳細（３）の14系列の中央値（平成30年度→令和7年度）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
@@ -3956,298 +3960,300 @@
       <c r="F31" s="6" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
+          <t>利用量による分</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>差（利用量以外の分）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>+1.51％</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>上の2つの差</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
           <t>報酬改定・加算の算定・要介護度の重度化による分</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>注）単価の伸び（年率+1.75％）のうち、利用量による分は+0.25％にとどまります。残り+1.51％は報酬改定・加算の算定・要介護度の重度化によるものです。改定の有無で単価の伸びに差が見られないことと合わせると、改定率を外から与えなくても、単価の実績の趨勢を置くことで実質的に改定を織り込めることになります。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>4　単価の置き方と月額</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>置き方</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>給付費（3か年）</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>差</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>① 令和7年度で固定（採用パターンP3）</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>+0.0％</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>+0.0％</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>9020.200000000001</v>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>6428円</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>+0円</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>② 実績の趨勢 年率+1.75％（平均）</t>
+          <t>① 令和7年度で固定（採用パターンP3）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>+3.5％</t>
+          <t>+0.0％</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>+7.2％</t>
+          <t>+0.0％</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>9505.5</v>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>6755円</t>
+        <v>9020.200000000001</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>6428円</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>+327円</t>
+          <t>+0円</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>③ 実績の趨勢 年率+1.32％（中央値）</t>
+          <t>② 実績の趨勢 年率+1.75％（平均）</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>+2.7％</t>
+          <t>+3.5％</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>+5.4％</t>
+          <t>+7.2％</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>9382.700000000001</v>
+        <v>9505.5</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>6672円</t>
+          <t>6755円</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>+244円</t>
+          <t>+327円</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>④ 年率＋1.0％</t>
+          <t>③ 実績の趨勢 年率+1.32％（中央値）</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>+2.0％</t>
+          <t>+2.7％</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>+4.1％</t>
+          <t>+5.4％</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>9294.5</v>
+        <v>9382.700000000001</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>6613円</t>
+          <t>6672円</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>+185円</t>
+          <t>+244円</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>④ 年率＋1.0％</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>+2.0％</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>+4.1％</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>9294.5</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>6613円</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>+185円</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>⑤ 年率＋2.0％</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>+4.0％</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>+8.2％</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E41" s="5" t="n">
         <v>9574.9</v>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>6802円</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>+374円</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>5　改定率のみを別に置く場合</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>改定率</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>給付費（3か年）</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>差</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>-0.50％</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>8975.1</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>6398円</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>-30円</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>+0.00％</t>
+          <t>-0.50％</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>9020.200000000001</v>
+        <v>8975.1</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>6428円</t>
+          <t>6398円</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>+0円</t>
+          <t>-30円</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
@@ -4257,20 +4263,20 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>+0.50％</t>
+          <t>+0.00％</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>9065.299999999999</v>
+        <v>9020.200000000001</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>6459円</t>
+          <t>6428円</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>+30円</t>
+          <t>+0円</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
@@ -4280,78 +4286,101 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>+1.00％</t>
+          <t>+0.50％</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>9110.4</v>
+        <v>9065.299999999999</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>6489円</t>
+          <t>6459円</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>+61円</t>
+          <t>+30円</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
       <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>改定率1％あたり月額+61円</t>
-        </is>
-      </c>
+      <c r="G47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>+1.50％</t>
+          <t>+1.00％</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>9155.5</v>
+        <v>9110.4</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>6519円</t>
+          <t>6489円</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>+91円</t>
+          <t>+61円</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
       <c r="F48" s="6" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>改定率1％あたり月額+61円</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>+2.00％</t>
+          <t>+1.50％</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>9200.6</v>
+        <v>9155.5</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>6550円</t>
+          <t>6519円</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>+121円</t>
+          <t>+91円</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr"/>
     </row>
-    <row r="50" ht="58" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>+2.00％</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>9200.6</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>6550円</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>+121円</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>注1）改定率1％あたり月額+61円です。
 注2）単価を令和7年度で固定したまま改定率のみを乗じる方法は、実績の趨勢（年率+1.75％）を落としたままになります。改定率が告示されたら、趨勢と改定率のどちらを採るかではなく、趨勢のうち改定による分と改定以外の分をどう分けるかの問題になります。
@@ -4361,17 +4390,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
